--- a/2024AIDataScienceGNRGeneral/Advanced Excel/feb8.xlsx
+++ b/2024AIDataScienceGNRGeneral/Advanced Excel/feb8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEBBA0D-C6C7-4C77-B3A1-5B75472A4084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A2F60E-898D-4619-ACC3-88A2704C2319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{503B1B66-BE0A-4E66-8B69-D21ECE4BD3E1}"/>
   </bookViews>
@@ -18,9 +18,14 @@
     <sheet name="Removing Duplicates 2" sheetId="4" r:id="rId3"/>
     <sheet name="Charts" sheetId="5" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
+  <definedNames>
+    <definedName name="_xlchart.v2.0" hidden="1">Charts!$D$2:$D$8</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Charts!$E$1</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Charts!$E$2:$E$8</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Charts!$D$2:$D$8</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">Charts!$E$1</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">Charts!$E$2:$E$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="70">
   <si>
     <t>DAF:</t>
   </si>
@@ -214,6 +219,33 @@
   </si>
   <si>
     <t>Sales in Lacs</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>Calls</t>
+  </si>
+  <si>
+    <t>Form Response</t>
+  </si>
+  <si>
+    <t>Demo Session</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Final Competition</t>
+  </si>
+  <si>
+    <t>Councelling</t>
+  </si>
+  <si>
+    <t>Admisssion</t>
   </si>
 </sst>
 </file>
@@ -286,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -295,6 +327,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -313,115 +348,2774 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="DAF"/>
-      <sheetName val="Removing Duplicates 1"/>
-      <sheetName val="Removing Duplicates 2"/>
-      <sheetName val="Charts"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>Sales in Lacs</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>2001</v>
-          </cell>
-          <cell r="B2">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2002</v>
-          </cell>
-          <cell r="B3">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2003</v>
-          </cell>
-          <cell r="B4">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>2004</v>
-          </cell>
-          <cell r="B5">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2005</v>
-          </cell>
-          <cell r="B6">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>2006</v>
-          </cell>
-          <cell r="B7">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>2007</v>
-          </cell>
-          <cell r="B8">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>2008</v>
-          </cell>
-          <cell r="B9">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>2009</v>
-          </cell>
-          <cell r="B10">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>2010</v>
-          </cell>
-          <cell r="B11">
-            <v>46</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:areaChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales in Lacs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="165100" prst="coolSlant"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Charts!$A$2:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2011</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$B$2:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97FE-4D0E-A77C-A86AD2A29F88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="601565624"/>
+        <c:axId val="601562024"/>
+      </c:areaChart>
+      <c:catAx>
+        <c:axId val="601565624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="601562024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="601562024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="601565624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="002060">
+              <a:alpha val="93000"/>
+            </a:srgbClr>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="165100" h="228600" prst="coolSlant"/>
+        </a:sp3d>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="20000"/>
+        <a:lumOff val="80000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:glow rad="139700">
+        <a:schemeClr val="accent2">
+          <a:satMod val="175000"/>
+          <a:alpha val="40000"/>
+        </a:schemeClr>
+      </a:glow>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d>
+      <a:bevelT w="139700" h="139700" prst="divot"/>
+    </a:sp3d>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Charts!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Numbers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="139700" h="139700" prst="divot"/>
+              <a:contourClr>
+                <a:srgbClr val="000000"/>
+              </a:contourClr>
+            </a:sp3d>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="30"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8026-4383-9279-692BBF4C4FFE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-8026-4383-9279-692BBF4C4FFE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-8026-4383-9279-692BBF4C4FFE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d contourW="25400">
+                <a:bevelT w="139700" h="139700" prst="divot"/>
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-8026-4383-9279-692BBF4C4FFE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.3704232049453158E-2"/>
+                  <c:y val="-3.7579857196542672E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-8026-4383-9279-692BBF4C4FFE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.7551117451260106E-3"/>
+                  <c:y val="-6.0127771514468242E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-8026-4383-9279-692BBF4C4FFE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.7551117451260103E-2"/>
+                  <c:y val="-5.2611800075159712E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-8026-4383-9279-692BBF4C4FFE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="70AD47">
+                  <a:lumMod val="50000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Charts!$D$2:$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Calls</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Form Response</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Demo Session</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Registration</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Final Competition</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Councelling</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Admisssion</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Charts!$E$2:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8026-4383-9279-692BBF4C4FFE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="20000"/>
+        <a:lumOff val="80000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </a:scene3d>
+    <a:sp3d>
+      <a:bevelT/>
+    </a:sp3d>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v2.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="funnel" uniqueId="{9998A601-A463-48E9-BFEB-619AEE98C7B1}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v2.1</cx:f>
+              <cx:v>Numbers</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="1">
+        <cx:catScaling gapWidth="0.0599999987"/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{122A23C3-FEAC-DF59-8AD4-DFCC20C4A238}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8503920" y="171450"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D602DA-A82F-E67E-E338-1E090C987C5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480745EE-E7E5-00E1-B045-3A4DF6CE2442}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1702,78 +4396,128 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDEF16F6-C08B-402F-B331-94BF9E9AF4D5}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2001</v>
       </c>
       <c r="B2">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2002</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2003</v>
       </c>
       <c r="B4">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2004</v>
       </c>
       <c r="B5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2005</v>
       </c>
       <c r="B6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2006</v>
       </c>
       <c r="B7">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2007</v>
       </c>
       <c r="B8">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -1781,7 +4525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2009</v>
       </c>
@@ -1789,7 +4533,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2010</v>
       </c>
@@ -1797,7 +4541,16 @@
         <v>46</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2011</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>